--- a/한국_2030_분야별_인지도_TOP100_총500인.xlsx
+++ b/한국_2030_분야별_인지도_TOP100_총500인.xlsx
@@ -839,22 +839,22 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>잔망루피</t>
+          <t>트랄랄레로 트랄랄라</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>뽀롱뽀롱 뽀로로 (스핀오프)</t>
+          <t>이탈리안 브레인롯 (Italian Brainrot)</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>인터넷 밈</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>카카오톡 이모티콘 1위, 2030 직장인 흑화/해탈 밈의 상징</t>
+          <t>나이키 신발을 신은 세 발 달린 상어, 이탈리안 브레인롯 밈 (Tralalero Tralala)</t>
         </is>
       </c>
     </row>
@@ -1739,22 +1739,22 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>핑구</t>
+          <t>퉁*9 사후르</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>꼬마펭귄 핑구</t>
+          <t>이탈리안 브레인롯 (Italian Brainrot)</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>스위스/영국</t>
+          <t>인터넷 밈</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>'눱눱!', 점토 클레이 애니메이션의 전설, 2030 추억의 짤</t>
+          <t>야구 방망이를 든 통나무 괴물, 퉁을 9번 외치는 이탈리안 브레인롯 밈 (Tung Tung... Sahur)</t>
         </is>
       </c>
     </row>
@@ -8656,12 +8656,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>너덜트</t>
+          <t>도파</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>스케치 코미디</t>
+          <t>게임 / 인터넷 방송</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>당근마켓 짤, 일상 속 웃픈 순간을 감각적인 편집으로 담아낸 코미디</t>
+          <t>LoL 천상계 미드 라이너이자 인터넷 방송인 (정상길), '압도', '도파'</t>
         </is>
       </c>
     </row>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>백종원 (PAIK JONG WON)</t>
+          <t>승우아빠</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>요리 레시피 / 음식 탐방</t>
+          <t>요리 레시피 / 음식 실험</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>자취생 초간단 레시피, 외식업 솔루션, 2030 요리 초보들의 구세주</t>
+          <t>에드워드 권 사단 셰프 출신 요리 크리에이터 (목진화), '세상의 모든 요리'</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>김하성</t>
+          <t>김창섭(신창섭)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>샌디에이고 파드리스 (야구)</t>
+          <t>넥슨 메이플스토리 총괄 디렉터</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>MLB 골드글러브 수상, 몸을 아끼지 않는 허슬 플레이로 2030 팬덤 확보</t>
+          <t>넥슨 메이플스토리 총괄 디렉터, '다 해줬잖아', '정상화' 밈의 주인공</t>
         </is>
       </c>
     </row>
@@ -12270,22 +12270,22 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>정의선</t>
+          <t>박나은 프로님</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>기업인</t>
+          <t>여</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>현대자동차그룹 회장</t>
+          <t>SSAFY 운영 프로</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>아이오닉·EV 시리즈 전기차 혁신, 2030 직장인 취업 선호도 1위</t>
+          <t>우리의 든든한 SSAFY 운영 프로님</t>
         </is>
       </c>
     </row>
@@ -12895,22 +12895,22 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>구본길</t>
+          <t>김준호 강사님</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>스포츠</t>
+          <t>남</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>펜싱 국가대표</t>
+          <t>SSAFY 담당 강사</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>어펜져스 맏형, 화려한 검술과 파이팅 넘치는 펜싱 스타</t>
+          <t>열정과 실력을 겸비한 SSAFY 담당 강사님</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>허훈</t>
+          <t>금강선(로스트아크 디렉터)</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>수원 KT 소닉붐 (농구)</t>
+          <t>스마일게이트 RPG CCO</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>농구 대통령 허재의 아들, 화려한 드리블과 득점력의 가드 스타</t>
+          <t>스마일게이트 RPG CCO, '빛강선', '로아온'의 전설적인 로스트아크 총괄 디렉터</t>
         </is>
       </c>
     </row>
